--- a/cet4/result/05_重生女帝_凤临天下/05_重生女帝_凤临天下_学习版.xlsx
+++ b/cet4/result/05_重生女帝_凤临天下/05_重生女帝_凤临天下_学习版.xlsx
@@ -397,787 +397,759 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D53"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>office</v>
       </c>
       <c r="B2" t="str">
-        <v>office</v>
+        <v>/ˈɑːfɪs/</v>
       </c>
       <c r="C2" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>办公室</v>
       </c>
-      <c r="D2" t="str">
-        <v>office(办公室)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>corporation</v>
       </c>
       <c r="B3" t="str">
-        <v>corporation</v>
+        <v>/ˌkɔːrpəˈreɪʃn/</v>
       </c>
       <c r="C3" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>公司</v>
       </c>
-      <c r="D3" t="str">
-        <v>corporation(公司)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>billion</v>
       </c>
       <c r="B4" t="str">
-        <v>billion</v>
+        <v>/ˈbɪljən/</v>
       </c>
       <c r="C4" t="str">
+        <v>n./adj./num.</v>
+      </c>
+      <c r="D4" t="str">
         <v>十亿</v>
       </c>
-      <c r="D4" t="str">
-        <v>billion(十亿)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>horizontal</v>
       </c>
       <c r="B5" t="str">
-        <v>horizontal</v>
+        <v>/ˌhɔːrɪˈzɑːntl/</v>
       </c>
       <c r="C5" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D5" t="str">
         <v>水平的</v>
       </c>
-      <c r="D5" t="str">
-        <v>horizontal(水平的)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>English</v>
       </c>
       <c r="B6" t="str">
-        <v>English</v>
+        <v>/ˈɪŋɡlɪʃ/</v>
       </c>
       <c r="C6" t="str">
+        <v>n./v./adj.</v>
+      </c>
+      <c r="D6" t="str">
         <v>英语</v>
       </c>
-      <c r="D6" t="str">
-        <v>English(英语)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>obtain</v>
       </c>
       <c r="B7" t="str">
-        <v>obtain</v>
+        <v>/əbˈteɪn/</v>
       </c>
       <c r="C7" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D7" t="str">
         <v>获得</v>
       </c>
-      <c r="D7" t="str">
-        <v>obtain(获得)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>handsome</v>
       </c>
       <c r="B8" t="str">
-        <v>handsome</v>
+        <v>/ˈhænsəm/</v>
       </c>
       <c r="C8" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D8" t="str">
         <v>英俊的</v>
       </c>
-      <c r="D8" t="str">
-        <v>handsome(英俊的)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>charming</v>
       </c>
       <c r="B9" t="str">
-        <v>charming</v>
+        <v>/ˈtʃɑːrmɪŋ/</v>
       </c>
       <c r="C9" t="str">
+        <v>v./adj.</v>
+      </c>
+      <c r="D9" t="str">
         <v>迷人的</v>
       </c>
-      <c r="D9" t="str">
-        <v>charming(迷人的)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>professional</v>
       </c>
       <c r="B10" t="str">
-        <v>professional</v>
+        <v>/prəˈfeʃənl/</v>
       </c>
       <c r="C10" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D10" t="str">
         <v>专业的</v>
       </c>
-      <c r="D10" t="str">
-        <v>professional(专业的)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>insist</v>
       </c>
       <c r="B11" t="str">
-        <v>insist</v>
+        <v>/ɪnˈsɪst/</v>
       </c>
       <c r="C11" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D11" t="str">
         <v>坚持</v>
       </c>
-      <c r="D11" t="str">
-        <v>insist(坚持)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>doubtful</v>
       </c>
       <c r="B12" t="str">
-        <v>doubtful</v>
+        <v>/ˈdaʊtfl/</v>
       </c>
       <c r="C12" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D12" t="str">
         <v>可疑的</v>
       </c>
-      <c r="D12" t="str">
-        <v>doubtful(可疑的)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>tide</v>
       </c>
       <c r="B13" t="str">
-        <v>tide</v>
+        <v>/taɪd/</v>
       </c>
       <c r="C13" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D13" t="str">
         <v>潮流</v>
       </c>
-      <c r="D13" t="str">
-        <v>tide(潮流)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>their</v>
       </c>
       <c r="B14" t="str">
-        <v>their</v>
+        <v>/ðer/</v>
       </c>
       <c r="C14" t="str">
+        <v>n./pron.</v>
+      </c>
+      <c r="D14" t="str">
         <v>他们的</v>
       </c>
-      <c r="D14" t="str">
-        <v>their(他们的)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>waggon</v>
       </c>
       <c r="B15" t="str">
-        <v>waggon</v>
+        <v>/ˈwæɡən/</v>
       </c>
       <c r="C15" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D15" t="str">
         <v>四轮运货马车</v>
       </c>
-      <c r="D15" t="str">
-        <v>waggon(四轮运货马车)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>canal</v>
       </c>
       <c r="B16" t="str">
-        <v>canal</v>
+        <v>/kəˈnæl/</v>
       </c>
       <c r="C16" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D16" t="str">
         <v>运河</v>
       </c>
-      <c r="D16" t="str">
-        <v>canal(运河)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>waterfall</v>
       </c>
       <c r="B17" t="str">
-        <v>waterfall</v>
+        <v>/ˈwɔːtərfɔːl/</v>
       </c>
       <c r="C17" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D17" t="str">
         <v>瀑布</v>
       </c>
-      <c r="D17" t="str">
-        <v>waterfall(瀑布)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>camp</v>
       </c>
       <c r="B18" t="str">
-        <v>camp</v>
+        <v>/kæmp/</v>
       </c>
       <c r="C18" t="str">
+        <v>n./vi.</v>
+      </c>
+      <c r="D18" t="str">
         <v>露营</v>
       </c>
-      <c r="D18" t="str">
-        <v>camp(露营)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>owl</v>
       </c>
       <c r="B19" t="str">
-        <v>owl</v>
+        <v>/aʊl/</v>
       </c>
       <c r="C19" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D19" t="str">
         <v>猫头鹰</v>
       </c>
-      <c r="D19" t="str">
-        <v>owl(猫头鹰)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>forget</v>
       </c>
       <c r="B20" t="str">
-        <v>forget</v>
+        <v>/fərˈɡet/</v>
       </c>
       <c r="C20" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D20" t="str">
         <v>忘记</v>
       </c>
-      <c r="D20" t="str">
-        <v>forget(忘记)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>log</v>
       </c>
       <c r="B21" t="str">
-        <v>log</v>
+        <v>/lɔːɡ/</v>
       </c>
       <c r="C21" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D21" t="str">
         <v>航行日志</v>
       </c>
-      <c r="D21" t="str">
-        <v>log(航行日志)📢</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>horse</v>
       </c>
       <c r="B22" t="str">
-        <v>horse</v>
+        <v>/hɔːrs/</v>
       </c>
       <c r="C22" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D22" t="str">
         <v>马</v>
       </c>
-      <c r="D22" t="str">
-        <v>horse(马)📢</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>dam</v>
       </c>
       <c r="B23" t="str">
-        <v>dam</v>
+        <v>/dæm/</v>
       </c>
       <c r="C23" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D23" t="str">
         <v>水坝</v>
       </c>
-      <c r="D23" t="str">
-        <v>dam(水坝)📢</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>underground</v>
       </c>
       <c r="B24" t="str">
-        <v>underground</v>
+        <v>/ˌʌndərˈɡraʊnd/</v>
       </c>
       <c r="C24" t="str">
+        <v>n./v./adj./adv.</v>
+      </c>
+      <c r="D24" t="str">
         <v>地下</v>
       </c>
-      <c r="D24" t="str">
-        <v>underground(地下)📢</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>consider</v>
       </c>
       <c r="B25" t="str">
-        <v>consider</v>
+        <v>/kənˈsɪdər/</v>
       </c>
       <c r="C25" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D25" t="str">
         <v>考虑</v>
       </c>
-      <c r="D25" t="str">
-        <v>consider(考虑)📢</v>
-      </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>organization</v>
       </c>
       <c r="B26" t="str">
-        <v>organization</v>
+        <v>/ˌɔːrɡənəˈzeɪʃn/</v>
       </c>
       <c r="C26" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D26" t="str">
         <v>组织</v>
       </c>
-      <c r="D26" t="str">
-        <v>organization(组织)📢</v>
-      </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>cable</v>
       </c>
       <c r="B27" t="str">
-        <v>cable</v>
+        <v>/ˈkeɪbl/</v>
       </c>
       <c r="C27" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D27" t="str">
         <v>电缆</v>
       </c>
-      <c r="D27" t="str">
-        <v>cable(电缆)📢</v>
-      </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>grade</v>
       </c>
       <c r="B28" t="str">
-        <v>grade</v>
+        <v>/ɡreɪd/</v>
       </c>
       <c r="C28" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D28" t="str">
         <v>等级</v>
       </c>
-      <c r="D28" t="str">
-        <v>grade(等级)📢</v>
-      </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>decent</v>
       </c>
       <c r="B29" t="str">
-        <v>decent</v>
+        <v>/ˈdiːsnt/</v>
       </c>
       <c r="C29" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D29" t="str">
         <v>正派的</v>
       </c>
-      <c r="D29" t="str">
-        <v>decent(正派的)📢</v>
-      </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>following</v>
       </c>
       <c r="B30" t="str">
-        <v>following</v>
+        <v>/ˈfɑːloʊɪŋ/</v>
       </c>
       <c r="C30" t="str">
+        <v>n./adj./prep.</v>
+      </c>
+      <c r="D30" t="str">
         <v>下列的</v>
       </c>
-      <c r="D30" t="str">
-        <v>following(下列的)📢</v>
-      </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>system</v>
       </c>
       <c r="B31" t="str">
-        <v>system</v>
+        <v>/ˈsɪstəm/</v>
       </c>
       <c r="C31" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D31" t="str">
         <v>系统</v>
       </c>
-      <c r="D31" t="str">
-        <v>system(系统)📢</v>
-      </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>scissors</v>
       </c>
       <c r="B32" t="str">
-        <v>scissors</v>
+        <v>/ˈsɪzərz/</v>
       </c>
       <c r="C32" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D32" t="str">
         <v>剪刀</v>
       </c>
-      <c r="D32" t="str">
-        <v>scissors(剪刀)📢</v>
-      </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>rot</v>
       </c>
       <c r="B33" t="str">
-        <v>rot</v>
+        <v>/rɑːt/</v>
       </c>
       <c r="C33" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D33" t="str">
         <v>腐烂</v>
       </c>
-      <c r="D33" t="str">
-        <v>rot(腐烂)📢</v>
-      </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>accidental</v>
       </c>
       <c r="B34" t="str">
-        <v>accidental</v>
+        <v>/ˌæksɪˈdentl/</v>
       </c>
       <c r="C34" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D34" t="str">
         <v>意外的</v>
       </c>
-      <c r="D34" t="str">
-        <v>accidental(意外的)📢</v>
-      </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>tutor</v>
       </c>
       <c r="B35" t="str">
-        <v>tutor</v>
+        <v>/ˈtuːtər/</v>
       </c>
       <c r="C35" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D35" t="str">
         <v>导师</v>
       </c>
-      <c r="D35" t="str">
-        <v>tutor(导师)📢</v>
-      </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>virtue</v>
       </c>
       <c r="B36" t="str">
-        <v>virtue</v>
+        <v>/ˈvɜːrtʃuː/</v>
       </c>
       <c r="C36" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D36" t="str">
         <v>美德</v>
       </c>
-      <c r="D36" t="str">
-        <v>virtue(美德)📢</v>
-      </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>firmly</v>
       </c>
       <c r="B37" t="str">
-        <v>firmly</v>
+        <v/>
       </c>
       <c r="C37" t="str">
+        <v/>
+      </c>
+      <c r="D37" t="str">
         <v>坚定地</v>
       </c>
-      <c r="D37" t="str">
-        <v>firmly(坚定地)📢</v>
-      </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>civilization</v>
       </c>
       <c r="B38" t="str">
-        <v>civilization</v>
+        <v>/ˌsɪvələˈzeɪʃn/</v>
       </c>
       <c r="C38" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D38" t="str">
         <v>文明</v>
       </c>
-      <c r="D38" t="str">
-        <v>civilization(文明)📢</v>
-      </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>contemporary</v>
       </c>
       <c r="B39" t="str">
-        <v>contemporary</v>
+        <v>/kənˈtempəreri/</v>
       </c>
       <c r="C39" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D39" t="str">
         <v>当代的</v>
       </c>
-      <c r="D39" t="str">
-        <v>contemporary(当代的)📢</v>
-      </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>foundation</v>
       </c>
       <c r="B40" t="str">
-        <v>foundation</v>
+        <v>/faʊnˈdeɪʃn/</v>
       </c>
       <c r="C40" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D40" t="str">
         <v>基础</v>
       </c>
-      <c r="D40" t="str">
-        <v>foundation(基础)📢</v>
-      </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>regular</v>
       </c>
       <c r="B41" t="str">
-        <v>regular</v>
+        <v>/ˈreɡjələr/</v>
       </c>
       <c r="C41" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D41" t="str">
         <v>定期的</v>
       </c>
-      <c r="D41" t="str">
-        <v>regular(定期的)📢</v>
-      </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>prescribe</v>
       </c>
       <c r="B42" t="str">
-        <v>prescribe</v>
+        <v>/prɪˈskraɪb/</v>
       </c>
       <c r="C42" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D42" t="str">
         <v>规定</v>
       </c>
-      <c r="D42" t="str">
-        <v>prescribe(规定)📢</v>
-      </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>just</v>
       </c>
       <c r="B43" t="str">
-        <v>just</v>
+        <v>/dʒʌst/</v>
       </c>
       <c r="C43" t="str">
+        <v>v./adj./adv.</v>
+      </c>
+      <c r="D43" t="str">
         <v>正义的</v>
       </c>
-      <c r="D43" t="str">
-        <v>just(正义的)📢</v>
-      </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>opinion</v>
       </c>
       <c r="B44" t="str">
-        <v>opinion</v>
+        <v>/əˈpɪnjən/</v>
       </c>
       <c r="C44" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D44" t="str">
         <v>意见</v>
       </c>
-      <c r="D44" t="str">
-        <v>opinion(意见)📢</v>
-      </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>appeal</v>
       </c>
       <c r="B45" t="str">
-        <v>appeal</v>
+        <v>/əˈpiːl/</v>
       </c>
       <c r="C45" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D45" t="str">
         <v>呼吁</v>
       </c>
-      <c r="D45" t="str">
-        <v>appeal(呼吁)📢</v>
-      </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>supplement</v>
       </c>
       <c r="B46" t="str">
-        <v>supplement</v>
+        <v>/ˈsʌplɪmənt/</v>
       </c>
       <c r="C46" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D46" t="str">
         <v>补充</v>
       </c>
-      <c r="D46" t="str">
-        <v>supplement(补充)📢</v>
-      </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>probability</v>
       </c>
       <c r="B47" t="str">
-        <v>their</v>
+        <v>/ˌprɑːbəˈbɪləti/</v>
       </c>
       <c r="C47" t="str">
-        <v>他们的</v>
+        <v>n.</v>
       </c>
       <c r="D47" t="str">
-        <v>their(他们的)📢</v>
+        <v>可能性</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>indicate</v>
       </c>
       <c r="B48" t="str">
-        <v>probability</v>
+        <v>/ˈɪndɪkeɪt/</v>
       </c>
       <c r="C48" t="str">
-        <v>可能性</v>
+        <v>vt.</v>
       </c>
       <c r="D48" t="str">
-        <v>probability(可能性)📢</v>
+        <v>表明</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>original</v>
       </c>
       <c r="B49" t="str">
-        <v>indicate</v>
+        <v>/əˈrɪdʒənl/</v>
       </c>
       <c r="C49" t="str">
-        <v>表明</v>
+        <v>n./adj.</v>
       </c>
       <c r="D49" t="str">
-        <v>indicate(表明)📢</v>
+        <v>原始的</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>shampoo</v>
       </c>
       <c r="B50" t="str">
-        <v>original</v>
+        <v>/ʃæmˈpuː/</v>
       </c>
       <c r="C50" t="str">
-        <v>原始的</v>
+        <v>n./vt.</v>
       </c>
       <c r="D50" t="str">
-        <v>original(原始的)📢</v>
+        <v>洗发精</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51">
-        <v>50</v>
+      <c r="A51" t="str">
+        <v>sew</v>
       </c>
       <c r="B51" t="str">
-        <v>civilization</v>
+        <v>/soʊ/</v>
       </c>
       <c r="C51" t="str">
-        <v>文明</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D51" t="str">
-        <v>civilization(文明)📢</v>
+        <v>缝合</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52">
-        <v>51</v>
+      <c r="A52" t="str">
+        <v>love</v>
       </c>
       <c r="B52" t="str">
-        <v>shampoo</v>
+        <v>/lʌv/</v>
       </c>
       <c r="C52" t="str">
-        <v>洗发精</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D52" t="str">
-        <v>shampoo(洗发精)📢</v>
+        <v>爱</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53">
-        <v>52</v>
+      <c r="A53" t="str">
+        <v>repetition</v>
       </c>
       <c r="B53" t="str">
-        <v>sew</v>
+        <v>/ˌrepəˈtɪʃn/</v>
       </c>
       <c r="C53" t="str">
-        <v>缝合</v>
+        <v>n.</v>
       </c>
       <c r="D53" t="str">
-        <v>sew(缝合)📢</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="str">
-        <v>love</v>
-      </c>
-      <c r="C54" t="str">
-        <v>爱</v>
-      </c>
-      <c r="D54" t="str">
-        <v>love(爱)📢</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="str">
-        <v>repetition</v>
-      </c>
-      <c r="C55" t="str">
         <v>重复</v>
-      </c>
-      <c r="D55" t="str">
-        <v>repetition(重复)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D55"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D53"/>
   </ignoredErrors>
 </worksheet>
 </file>